--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28441.03</v>
+        <v>28759.1</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3721.91</v>
+        <v>3698.83</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3613.2</v>
+        <v>3590.8</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2419.56</v>
+        <v>2387.33</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2395.6</v>
+        <v>2348.71</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>76659.10000000001</v>
+        <v>75083.63</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45742.47</v>
+        <v>45477.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -938,6 +938,372 @@
         <v>45477.7</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1171142-2748-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>62.000.830-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>3737.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1171142-2749-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>62.000.830-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2429.11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1057389-3767-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.602.229-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2632.04</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1952-2133-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>5805.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1952-2135-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>14564.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1952-2262-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>15364.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1171142-2748-CM26</t>
+          <t>1171142-2749-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3737.1</v>
+        <v>2429.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1171142-2749-CM26</t>
+          <t>1171142-2748-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2429.11</v>
+        <v>3737.1</v>
       </c>
     </row>
     <row r="11">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1302,6 +1302,250 @@
       </c>
       <c r="M14" s="2" t="n">
         <v>15364.28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1380-11059-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2320.18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1979-4226-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.607.401-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE NUEVA IMPERIAL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>2363.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1380-11351-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>2302.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1171142-3234-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>62.000.830-3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>6013.97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
@@ -745,7 +745,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1420,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +814,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +879,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -945,7 +957,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1171142-2749-CM26</t>
+          <t>1171142-2748-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1000,13 +1012,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2429.11</v>
+        <v>3737.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1171142-2748-CM26</t>
+          <t>1171142-2749-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1061,7 +1073,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3737.1</v>
+        <v>2429.11</v>
       </c>
     </row>
     <row r="11">
@@ -1546,7 +1558,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1554,6 +1570,250 @@
       </c>
       <c r="M18" s="2" t="n">
         <v>6013.97</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1952-2453-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>17924.08</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1952-2452-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>6739.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1952-2513-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>12911.89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1171142-3628-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>62.000.830-3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>3494.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1952-1225-CM26</t>
+          <t>1952-1368-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3698.83</v>
+        <v>3590.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1952-1368-CM26</t>
+          <t>1952-1225-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3590.8</v>
+        <v>3698.83</v>
       </c>
     </row>
     <row r="5">
@@ -896,7 +896,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1952-1929-CM26</t>
+          <t>1380-8310-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -911,22 +911,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -936,28 +936,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45477.7</v>
+        <v>15045.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1171142-2748-CM26</t>
+          <t>1952-1929-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -967,27 +971,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.830-3</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -997,12 +1001,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1012,13 +1016,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3737.1</v>
+        <v>45477.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1171142-2749-CM26</t>
+          <t>1171142-2748-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1073,13 +1077,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2429.11</v>
+        <v>3737.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057389-3767-CM26</t>
+          <t>1171142-2749-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1094,7 +1098,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1104,12 +1108,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>62.000.830-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1134,13 +1138,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2632.04</v>
+        <v>2429.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1952-2133-CM26</t>
+          <t>1057389-3767-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1155,7 +1159,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1180,12 +1184,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1195,13 +1199,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5805.23</v>
+        <v>2632.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1952-2135-CM26</t>
+          <t>1952-2133-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1256,13 +1260,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14564.55</v>
+        <v>5805.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1952-2262-CM26</t>
+          <t>1952-2135-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1277,7 +1281,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1317,13 +1321,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>15364.28</v>
+        <v>14564.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1380-11059-CM26</t>
+          <t>1952-2262-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1333,12 +1337,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1348,12 +1352,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1363,12 +1367,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1378,13 +1382,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2320.18</v>
+        <v>15364.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1979-4226-CM26</t>
+          <t>1380-11059-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1399,7 +1403,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1409,12 +1413,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.607.401-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE NUEVA IMPERIAL</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1424,32 +1428,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2363.06</v>
+        <v>2320.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1380-11351-CM26</t>
+          <t>1979-4226-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.607.401-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1489,28 +1489,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2302.7</v>
+        <v>2363.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1171142-3234-CM26</t>
+          <t>1380-11351-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1525,7 +1529,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1535,12 +1539,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.830-3</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1550,32 +1554,28 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6013.97</v>
+        <v>2302.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1952-2453-CM26</t>
+          <t>1171142-3234-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>62.000.830-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1615,28 +1615,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17924.08</v>
+        <v>6013.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1952-2452-CM26</t>
+          <t>1952-2453-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,13 +1695,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6739.57</v>
+        <v>17924.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1952-2513-CM26</t>
+          <t>1952-2452-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1712,12 +1716,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1737,12 +1741,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1752,13 +1756,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12911.89</v>
+        <v>6739.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1171142-3628-CM26</t>
+          <t>1952-2513-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1773,7 +1777,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1783,12 +1787,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.000.830-3</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1798,12 +1802,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1813,6 +1817,67 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
+        <v>12911.89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1171142-3628-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>62.000.830-3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>3494.7</v>
       </c>
     </row>
